--- a/output/lettera5.xlsx
+++ b/output/lettera5.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="243">
   <si>
     <t>word</t>
   </si>
@@ -25,682 +25,724 @@
     <t>lemma</t>
   </si>
   <si>
-    <t>Honorande</t>
-  </si>
-  <si>
-    <t>frater</t>
-  </si>
-  <si>
-    <t>etc</t>
-  </si>
-  <si>
-    <t>Hier</t>
-  </si>
-  <si>
-    <t>sera</t>
-  </si>
-  <si>
-    <t>colla</t>
-  </si>
-  <si>
-    <t>gratia</t>
+    <t>Magnifico</t>
+  </si>
+  <si>
+    <t>messer</t>
+  </si>
+  <si>
+    <t>Francesco</t>
+  </si>
+  <si>
+    <t>honorando</t>
+  </si>
+  <si>
+    <t>Per</t>
+  </si>
+  <si>
+    <t>le</t>
+  </si>
+  <si>
+    <t>mani</t>
   </si>
   <si>
     <t>di</t>
   </si>
   <si>
-    <t>Dio</t>
-  </si>
-  <si>
-    <t>ci</t>
-  </si>
-  <si>
-    <t>fu</t>
-  </si>
-  <si>
-    <t>lectere</t>
+    <t>Giovani</t>
+  </si>
+  <si>
+    <t>Caccini</t>
+  </si>
+  <si>
+    <t>ho</t>
+  </si>
+  <si>
+    <t>auto</t>
+  </si>
+  <si>
+    <t>una</t>
+  </si>
+  <si>
+    <t>vostra</t>
+  </si>
+  <si>
+    <t>In</t>
+  </si>
+  <si>
+    <t>risposta</t>
+  </si>
+  <si>
+    <t>dessa</t>
+  </si>
+  <si>
+    <t>dico</t>
+  </si>
+  <si>
+    <t>che</t>
+  </si>
+  <si>
+    <t>riceuto</t>
+  </si>
+  <si>
+    <t>laltra</t>
+  </si>
+  <si>
+    <t>co</t>
+  </si>
+  <si>
+    <t>migliaia</t>
+  </si>
+  <si>
+    <t>misti</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>pagato</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>noli</t>
+  </si>
+  <si>
+    <t>ancora</t>
+  </si>
+  <si>
+    <t>cavalli</t>
+  </si>
+  <si>
+    <t>quegli</t>
+  </si>
+  <si>
+    <t>Quelo</t>
+  </si>
+  <si>
+    <t>detto</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>Giovanni</t>
+  </si>
+  <si>
+    <t>dirò</t>
+  </si>
+  <si>
+    <t>voi</t>
+  </si>
+  <si>
+    <t>questi</t>
+  </si>
+  <si>
+    <t>barcaiuli</t>
+  </si>
+  <si>
+    <t>navicellai</t>
+  </si>
+  <si>
+    <t>sono</t>
+  </si>
+  <si>
+    <t>avezi</t>
+  </si>
+  <si>
+    <t>male</t>
+  </si>
+  <si>
+    <t>perché</t>
+  </si>
+  <si>
+    <t>vengono</t>
+  </si>
+  <si>
+    <t>qua</t>
+  </si>
+  <si>
+    <t>strilono</t>
+  </si>
+  <si>
+    <t>tanto</t>
+  </si>
+  <si>
+    <t>vinti</t>
+  </si>
+  <si>
+    <t>dal</t>
+  </si>
+  <si>
+    <t>fastidio</t>
+  </si>
+  <si>
+    <t>sia</t>
+  </si>
+  <si>
+    <t>dà</t>
+  </si>
+  <si>
+    <t>loro</t>
+  </si>
+  <si>
+    <t>più</t>
+  </si>
+  <si>
+    <t>non</t>
+  </si>
+  <si>
+    <t>meritano</t>
+  </si>
+  <si>
+    <t>sempre</t>
+  </si>
+  <si>
+    <t>vanno</t>
+  </si>
+  <si>
+    <t>allo</t>
+  </si>
+  <si>
+    <t>insù</t>
+  </si>
+  <si>
+    <t>talmente</t>
+  </si>
+  <si>
+    <t>vogliono</t>
+  </si>
+  <si>
+    <t>poi</t>
+  </si>
+  <si>
+    <t>calare</t>
+  </si>
+  <si>
+    <t>dicono</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
+    <t>desti</t>
+  </si>
+  <si>
+    <t>È</t>
+  </si>
+  <si>
+    <t>peggio</t>
+  </si>
+  <si>
+    <t>lamentare</t>
+  </si>
+  <si>
+    <t>Pisa</t>
+  </si>
+  <si>
+    <t>per</t>
+  </si>
+  <si>
+    <t>scusarsi</t>
+  </si>
+  <si>
+    <t>mostrare</t>
+  </si>
+  <si>
+    <t>volere</t>
+  </si>
+  <si>
+    <t>servire</t>
+  </si>
+  <si>
+    <t>taleché</t>
+  </si>
+  <si>
+    <t>tutti</t>
+  </si>
+  <si>
+    <t>noi</t>
+  </si>
+  <si>
+    <t>ministri</t>
+  </si>
+  <si>
+    <t>siamo</t>
+  </si>
+  <si>
+    <t>posti</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>croce</t>
   </si>
   <si>
     <t>da</t>
   </si>
   <si>
-    <t>Piero</t>
-  </si>
-  <si>
-    <t>le</t>
-  </si>
-  <si>
-    <t>quali</t>
-  </si>
-  <si>
-    <t>erano</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>dì</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>tenute</t>
-  </si>
-  <si>
-    <t>insino</t>
-  </si>
-  <si>
-    <t>a’</t>
-  </si>
-  <si>
-    <t>per</t>
-  </si>
-  <si>
-    <t>avisava</t>
-  </si>
-  <si>
-    <t>come</t>
+    <t>tale</t>
+  </si>
+  <si>
+    <t>canaglie</t>
+  </si>
+  <si>
+    <t>però</t>
+  </si>
+  <si>
+    <t>sarei</t>
+  </si>
+  <si>
+    <t>parere</t>
+  </si>
+  <si>
+    <t>quando</t>
+  </si>
+  <si>
+    <t>sentite</t>
+  </si>
+  <si>
+    <t>uno</t>
+  </si>
+  <si>
+    <t>lamenta</t>
+  </si>
+  <si>
+    <t>torto</t>
   </si>
   <si>
     <t>lo</t>
   </si>
   <si>
-    <t>imperadore</t>
-  </si>
-  <si>
-    <t>veduto</t>
-  </si>
-  <si>
-    <t>non</t>
-  </si>
-  <si>
-    <t>potere</t>
-  </si>
-  <si>
-    <t>piglare</t>
-  </si>
-  <si>
-    <t>Padova</t>
-  </si>
-  <si>
-    <t>dubitando</t>
-  </si>
-  <si>
-    <t>che</t>
-  </si>
-  <si>
-    <t>nel</t>
-  </si>
-  <si>
-    <t>soprastare</t>
-  </si>
-  <si>
-    <t>sia</t>
-  </si>
-  <si>
-    <t>guastassi</t>
-  </si>
-  <si>
-    <t>el</t>
-  </si>
-  <si>
-    <t>tempo</t>
-  </si>
-  <si>
-    <t>et</t>
-  </si>
-  <si>
-    <t>impedissi</t>
-  </si>
-  <si>
-    <t>salvare</t>
-  </si>
-  <si>
-    <t>artiglerie</t>
-  </si>
-  <si>
-    <t>era</t>
+    <t>fareti</t>
+  </si>
+  <si>
+    <t>gastigare</t>
+  </si>
+  <si>
+    <t>misure</t>
+  </si>
+  <si>
+    <t>carboni</t>
+  </si>
+  <si>
+    <t>esemplo</t>
+  </si>
+  <si>
+    <t>degli</t>
+  </si>
+  <si>
+    <t>altri</t>
+  </si>
+  <si>
+    <t>Questi</t>
+  </si>
+  <si>
+    <t>ànno</t>
+  </si>
+  <si>
+    <t>de</t>
+  </si>
+  <si>
+    <t>scudo</t>
+  </si>
+  <si>
+    <t>del</t>
+  </si>
+  <si>
+    <t>migliaio</t>
+  </si>
+  <si>
+    <t>cosa</t>
+  </si>
+  <si>
+    <t>certo</t>
+  </si>
+  <si>
+    <t>ingorda</t>
+  </si>
+  <si>
+    <t>mal</t>
+  </si>
+  <si>
+    <t>fatta</t>
+  </si>
+  <si>
+    <t>sio</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>avevo</t>
+  </si>
+  <si>
+    <t>aviso</t>
+  </si>
+  <si>
+    <t>trentasei</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>li</t>
+  </si>
+  <si>
+    <t>davo</t>
+  </si>
+  <si>
+    <t>mai</t>
+  </si>
+  <si>
+    <t>dite</t>
+  </si>
+  <si>
+    <t>vilania</t>
+  </si>
+  <si>
+    <t>Messer</t>
+  </si>
+  <si>
+    <t>ha</t>
+  </si>
+  <si>
+    <t>far</t>
+  </si>
+  <si>
+    <t>fare</t>
+  </si>
+  <si>
+    <t>stadera</t>
+  </si>
+  <si>
+    <t>pesare</t>
+  </si>
+  <si>
+    <t>piace</t>
+  </si>
+  <si>
+    <t>assai</t>
+  </si>
+  <si>
+    <t>ne</t>
+  </si>
+  <si>
+    <t>staremo</t>
+  </si>
+  <si>
+    <t>bene</t>
+  </si>
+  <si>
+    <t>senza</t>
+  </si>
+  <si>
+    <t>biasimo</t>
+  </si>
+  <si>
+    <t>ser</t>
+  </si>
+  <si>
+    <t>Iacomo</t>
+  </si>
+  <si>
+    <t>credo</t>
+  </si>
+  <si>
+    <t>oggi</t>
+  </si>
+  <si>
+    <t>abbia</t>
+  </si>
+  <si>
+    <t>rimesso</t>
+  </si>
+  <si>
+    <t>danari</t>
+  </si>
+  <si>
+    <t>cioè</t>
+  </si>
+  <si>
+    <t>scudi</t>
+  </si>
+  <si>
+    <t>moneta</t>
+  </si>
+  <si>
+    <t>così</t>
+  </si>
+  <si>
+    <t>farà</t>
+  </si>
+  <si>
+    <t>vi</t>
+  </si>
+  <si>
+    <t>prego</t>
+  </si>
+  <si>
+    <t>agevoliate</t>
+  </si>
+  <si>
+    <t>negoti</t>
+  </si>
+  <si>
+    <t>aviseremo</t>
+  </si>
+  <si>
+    <t>servino</t>
+  </si>
+  <si>
+    <t>eccellenze</t>
+  </si>
+  <si>
+    <t>farò</t>
+  </si>
+  <si>
+    <t>io</t>
+  </si>
+  <si>
+    <t>se</t>
+  </si>
+  <si>
+    <t>comanderete</t>
+  </si>
+  <si>
+    <t>Altro</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>eccellenza</t>
+  </si>
+  <si>
+    <t>fine</t>
+  </si>
+  <si>
+    <t>racomando</t>
+  </si>
+  <si>
+    <t>Di</t>
+  </si>
+  <si>
+    <t>Firenze</t>
+  </si>
+  <si>
+    <t>agli</t>
+  </si>
+  <si>
+    <t>XXII</t>
+  </si>
+  <si>
+    <t>Gennaio</t>
+  </si>
+  <si>
+    <t>signoria</t>
+  </si>
+  <si>
+    <t>amorevole</t>
+  </si>
+  <si>
+    <t>amico</t>
+  </si>
+  <si>
+    <t>ADJ</t>
+  </si>
+  <si>
+    <t>NOM</t>
+  </si>
+  <si>
+    <t>NPR</t>
+  </si>
+  <si>
+    <t>VER:geru</t>
+  </si>
+  <si>
+    <t>PRE</t>
+  </si>
+  <si>
+    <t>DET:def</t>
+  </si>
+  <si>
+    <t>VER:pres</t>
+  </si>
+  <si>
+    <t>DET:indef</t>
+  </si>
+  <si>
+    <t>PRO:poss</t>
+  </si>
+  <si>
+    <t>PRO:rela</t>
+  </si>
+  <si>
+    <t>VER:pper</t>
+  </si>
+  <si>
+    <t>CON</t>
+  </si>
+  <si>
+    <t>ADV</t>
+  </si>
+  <si>
+    <t>PRO:demo</t>
+  </si>
+  <si>
+    <t>VER:futu</t>
+  </si>
+  <si>
+    <t>VER:impe</t>
+  </si>
+  <si>
+    <t>PRE:det</t>
+  </si>
+  <si>
+    <t>PRO:pers</t>
+  </si>
+  <si>
+    <t>VER:infi</t>
+  </si>
+  <si>
+    <t>VER:cpre</t>
+  </si>
+  <si>
+    <t>VER:cond</t>
+  </si>
+  <si>
+    <t>VER:impf</t>
+  </si>
+  <si>
+    <t>PRO:refl</t>
+  </si>
+  <si>
+    <t>NUM</t>
+  </si>
+  <si>
+    <t>magnifico</t>
+  </si>
+  <si>
+    <t>il</t>
+  </si>
+  <si>
+    <t>mano</t>
+  </si>
+  <si>
+    <t>giovane</t>
+  </si>
+  <si>
+    <t>avere</t>
+  </si>
+  <si>
+    <t>vostro</t>
+  </si>
+  <si>
+    <t>dire</t>
+  </si>
+  <si>
+    <t>misto</t>
+  </si>
+  <si>
+    <t>pagare</t>
+  </si>
+  <si>
+    <t>nolo</t>
+  </si>
+  <si>
+    <t>cavallo</t>
+  </si>
+  <si>
+    <t>quello</t>
+  </si>
+  <si>
+    <t>questo</t>
+  </si>
+  <si>
+    <t>essere</t>
+  </si>
+  <si>
+    <t>venire</t>
+  </si>
+  <si>
+    <t>vincere</t>
+  </si>
+  <si>
+    <t>dare</t>
+  </si>
+  <si>
+    <t>meritare</t>
+  </si>
+  <si>
+    <t>andare</t>
   </si>
   <si>
     <t>al</t>
   </si>
   <si>
-    <t>primo</t>
-  </si>
-  <si>
-    <t>octobre</t>
-  </si>
-  <si>
-    <t>levato</t>
-  </si>
-  <si>
-    <t>campo</t>
-  </si>
-  <si>
-    <t>ritractosi</t>
-  </si>
-  <si>
-    <t>Limini</t>
-  </si>
-  <si>
-    <t>luogo</t>
-  </si>
-  <si>
-    <t>presso</t>
-  </si>
-  <si>
-    <t>quivi</t>
-  </si>
-  <si>
-    <t>migla</t>
-  </si>
-  <si>
-    <t>con</t>
-  </si>
-  <si>
-    <t>animo</t>
-  </si>
-  <si>
-    <t>ritrarsi</t>
-  </si>
-  <si>
-    <t>alla</t>
-  </si>
-  <si>
-    <t>volta</t>
-  </si>
-  <si>
-    <t>Vicentia</t>
-  </si>
-  <si>
-    <t>Quelle</t>
-  </si>
-  <si>
-    <t>del</t>
-  </si>
-  <si>
-    <t>Publico</t>
-  </si>
-  <si>
-    <t>sono</t>
-  </si>
-  <si>
-    <t>dove</t>
-  </si>
-  <si>
-    <t>avisano</t>
-  </si>
-  <si>
-    <t>essersi</t>
-  </si>
-  <si>
-    <t>ritirati</t>
-  </si>
-  <si>
-    <t>poche</t>
-  </si>
-  <si>
-    <t>né</t>
-  </si>
-  <si>
-    <t>sapere</t>
-  </si>
-  <si>
-    <t>suo</t>
-  </si>
-  <si>
-    <t>fare</t>
-  </si>
-  <si>
-    <t>benché</t>
-  </si>
-  <si>
-    <t>intendono</t>
-  </si>
-  <si>
-    <t>fa</t>
-  </si>
-  <si>
-    <t>ogni</t>
-  </si>
-  <si>
-    <t>cosa</t>
-  </si>
-  <si>
-    <t>nuovi</t>
-  </si>
-  <si>
-    <t>danari</t>
-  </si>
-  <si>
-    <t>strade</t>
-  </si>
-  <si>
-    <t>essere</t>
-  </si>
-  <si>
-    <t>rocte</t>
-  </si>
-  <si>
-    <t>tucto</t>
-  </si>
-  <si>
-    <t>però</t>
-  </si>
-  <si>
-    <t>soprastato</t>
-  </si>
-  <si>
-    <t>tanto</t>
-  </si>
-  <si>
-    <t>passare</t>
-  </si>
-  <si>
-    <t>cavallaro</t>
-  </si>
-  <si>
-    <t>dello</t>
-  </si>
-  <si>
-    <t>accordo</t>
-  </si>
-  <si>
-    <t>havere</t>
-  </si>
-  <si>
-    <t>poi</t>
-  </si>
-  <si>
-    <t>tractato</t>
+    <t>destare</t>
+  </si>
+  <si>
+    <t>scusare</t>
+  </si>
+  <si>
+    <t>tutto</t>
+  </si>
+  <si>
+    <t>ministro</t>
+  </si>
+  <si>
+    <t>porre</t>
+  </si>
+  <si>
+    <t>canaglia</t>
+  </si>
+  <si>
+    <t>sentito</t>
+  </si>
+  <si>
+    <t>misura</t>
+  </si>
+  <si>
+    <t>carbone</t>
   </si>
   <si>
     <t>altro</t>
   </si>
   <si>
-    <t>perché</t>
-  </si>
-  <si>
-    <t>ancora</t>
-  </si>
-  <si>
-    <t>comparito</t>
-  </si>
-  <si>
-    <t>Zerino</t>
-  </si>
-  <si>
-    <t>Ardingo</t>
-  </si>
-  <si>
-    <t>portorono</t>
-  </si>
-  <si>
-    <t>la</t>
-  </si>
-  <si>
-    <t>commessione</t>
-  </si>
-  <si>
-    <t>quello</t>
-  </si>
-  <si>
-    <t>havessino</t>
-  </si>
-  <si>
-    <t>Questo</t>
-  </si>
-  <si>
-    <t>è</t>
-  </si>
-  <si>
-    <t>quanto</t>
-  </si>
-  <si>
-    <t>avisono</t>
-  </si>
-  <si>
-    <t>io</t>
-  </si>
-  <si>
-    <t>habbia</t>
-  </si>
-  <si>
-    <t>inteso</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>qui</t>
-  </si>
-  <si>
-    <t>stamane</t>
-  </si>
-  <si>
-    <t>s’è</t>
-  </si>
-  <si>
-    <t>spacciato</t>
-  </si>
-  <si>
-    <t>uno</t>
-  </si>
-  <si>
-    <t>Hieri</t>
-  </si>
-  <si>
-    <t>cavallo</t>
-  </si>
-  <si>
-    <t>Ferrara</t>
-  </si>
-  <si>
-    <t>Iacopo</t>
-  </si>
-  <si>
-    <t>madonna</t>
-  </si>
-  <si>
-    <t>Simona</t>
-  </si>
-  <si>
-    <t>voi</t>
-  </si>
-  <si>
-    <t>saranno</t>
-  </si>
-  <si>
-    <t>questa</t>
-  </si>
-  <si>
-    <t>stamani</t>
-  </si>
-  <si>
-    <t>hebbi</t>
-  </si>
-  <si>
-    <t>delli</t>
-  </si>
-  <si>
-    <t>XI</t>
-  </si>
-  <si>
-    <t>avisa</t>
-  </si>
-  <si>
-    <t>trovarsi</t>
-  </si>
-  <si>
-    <t>in</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
-    <t>v’haveva</t>
-  </si>
-  <si>
-    <t>dato</t>
-  </si>
-  <si>
-    <t>aviso</t>
-  </si>
-  <si>
-    <t>partirebbe</t>
-  </si>
-  <si>
-    <t>havessi</t>
-  </si>
-  <si>
-    <t>lui</t>
-  </si>
-  <si>
-    <t>haveva</t>
-  </si>
-  <si>
-    <t>Partissi</t>
-  </si>
-  <si>
-    <t>intendendo</t>
-  </si>
-  <si>
-    <t>rocta</t>
-  </si>
-  <si>
-    <t>quella</t>
-  </si>
-  <si>
-    <t>strada</t>
-  </si>
-  <si>
-    <t>pensò</t>
-  </si>
-  <si>
-    <t>cavallari</t>
-  </si>
-  <si>
-    <t>altra</t>
-  </si>
-  <si>
-    <t>via</t>
-  </si>
-  <si>
-    <t>volere</t>
-  </si>
-  <si>
-    <t>scrivere</t>
-  </si>
-  <si>
-    <t>risposta</t>
-  </si>
-  <si>
-    <t>fussi</t>
-  </si>
-  <si>
-    <t>più</t>
-  </si>
-  <si>
-    <t>commodo</t>
-  </si>
-  <si>
-    <t>inoltre</t>
-  </si>
-  <si>
-    <t>se</t>
-  </si>
-  <si>
-    <t>intendessi</t>
-  </si>
-  <si>
-    <t>là</t>
-  </si>
-  <si>
-    <t>sicure</t>
-  </si>
-  <si>
-    <t>andare</t>
-  </si>
-  <si>
-    <t>trovare</t>
-  </si>
-  <si>
-    <t>il</t>
-  </si>
-  <si>
-    <t>ha</t>
-  </si>
-  <si>
-    <t>facto</t>
-  </si>
-  <si>
-    <t>pericolo</t>
-  </si>
-  <si>
-    <t>Altro</t>
-  </si>
-  <si>
-    <t>accade</t>
-  </si>
-  <si>
-    <t>In</t>
-  </si>
-  <si>
-    <t>Firenze</t>
-  </si>
-  <si>
-    <t>NOM</t>
-  </si>
-  <si>
-    <t>ADJ</t>
-  </si>
-  <si>
-    <t>PRE:det</t>
-  </si>
-  <si>
-    <t>PRE</t>
-  </si>
-  <si>
-    <t>NPR</t>
-  </si>
-  <si>
-    <t>PRO:refl</t>
-  </si>
-  <si>
-    <t>VER:remo</t>
-  </si>
-  <si>
-    <t>VER:infi</t>
-  </si>
-  <si>
-    <t>DET:def</t>
-  </si>
-  <si>
-    <t>PRO:rela</t>
-  </si>
-  <si>
-    <t>VER:impf</t>
-  </si>
-  <si>
-    <t>VER:pper</t>
-  </si>
-  <si>
-    <t>CON</t>
-  </si>
-  <si>
-    <t>VER:cpre</t>
-  </si>
-  <si>
-    <t>ADV</t>
-  </si>
-  <si>
-    <t>VER:geru</t>
-  </si>
-  <si>
-    <t>VER:cimp</t>
-  </si>
-  <si>
-    <t>PRO:pers</t>
-  </si>
-  <si>
-    <t>PRO:demo</t>
-  </si>
-  <si>
-    <t>VER:pres</t>
-  </si>
-  <si>
-    <t>VER:impe</t>
-  </si>
-  <si>
-    <t>PRO:poss</t>
-  </si>
-  <si>
-    <t>DET:indef</t>
-  </si>
-  <si>
-    <t>VER:futu</t>
-  </si>
-  <si>
-    <t>NUM</t>
-  </si>
-  <si>
-    <t>VER:cond</t>
-  </si>
-  <si>
-    <t>col</t>
-  </si>
-  <si>
-    <t>quale</t>
-  </si>
-  <si>
-    <t>dare</t>
-  </si>
-  <si>
-    <t>tenuta</t>
-  </si>
-  <si>
-    <t>vedere</t>
-  </si>
-  <si>
-    <t>dubitare</t>
-  </si>
-  <si>
-    <t>guastare</t>
-  </si>
-  <si>
-    <t>impedire</t>
-  </si>
-  <si>
-    <t>levare</t>
-  </si>
-  <si>
-    <t>limine</t>
-  </si>
-  <si>
-    <t>ritrarre</t>
-  </si>
-  <si>
-    <t>tenere</t>
-  </si>
-  <si>
-    <t>ritirare</t>
-  </si>
-  <si>
-    <t>poco</t>
-  </si>
-  <si>
-    <t>intendere</t>
-  </si>
-  <si>
-    <t>nuovo</t>
+    <t>ingordo</t>
+  </si>
+  <si>
+    <t>nono</t>
+  </si>
+  <si>
+    <t>piacere</t>
+  </si>
+  <si>
+    <t>stare</t>
+  </si>
+  <si>
+    <t>credere</t>
+  </si>
+  <si>
+    <t>rimettere</t>
   </si>
   <si>
     <t>danaro</t>
   </si>
   <si>
-    <t>questo</t>
-  </si>
-  <si>
-    <t>spacciare</t>
-  </si>
-  <si>
-    <t>partire</t>
-  </si>
-  <si>
-    <t>pensare</t>
-  </si>
-  <si>
-    <t>sicuro</t>
-  </si>
-  <si>
-    <t>avere</t>
-  </si>
-  <si>
-    <t>accadere</t>
+    <t>pregare</t>
+  </si>
+  <si>
+    <t>agevolare</t>
+  </si>
+  <si>
+    <t>comandare</t>
+  </si>
+  <si>
+    <t>gennaio</t>
   </si>
 </sst>
 </file>
@@ -1058,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C307"/>
+  <dimension ref="A1:C274"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1077,10 +1119,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1088,7 +1130,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -1110,7 +1152,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1121,10 +1163,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1132,10 +1174,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1146,7 +1188,7 @@
         <v>179</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1162,329 +1204,329 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C16" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C17" t="s">
-        <v>206</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C19" t="s">
-        <v>207</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C23" t="s">
-        <v>208</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C27" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C28" t="s">
-        <v>206</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C31" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
+        <v>203</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C33" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C34" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C36" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C37" t="s">
-        <v>36</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C39" t="s">
         <v>210</v>
@@ -1492,321 +1534,321 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C40" t="s">
-        <v>38</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B41" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C41" t="s">
-        <v>39</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C42" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C43" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B44" t="s">
         <v>191</v>
       </c>
       <c r="C44" t="s">
-        <v>41</v>
+        <v>213</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B45" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="C45" t="s">
-        <v>211</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C46" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B48" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C48" t="s">
-        <v>45</v>
+        <v>208</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B49" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="C50" t="s">
-        <v>212</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B51" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B52" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C52" t="s">
-        <v>47</v>
+        <v>208</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B53" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C53" t="s">
-        <v>171</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B54" t="s">
         <v>179</v>
       </c>
       <c r="C54" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="B55" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C55" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C56" t="s">
-        <v>49</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B57" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C57" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C58" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B59" t="s">
         <v>179</v>
       </c>
       <c r="C59" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="B60" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C60" t="s">
-        <v>10</v>
+        <v>215</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B61" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="C61" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
         <v>190</v>
       </c>
       <c r="C62" t="s">
-        <v>213</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B63" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C63" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B64" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C64" t="s">
-        <v>54</v>
+        <v>216</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B65" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C65" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C66" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="B67" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C67" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B68" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C68" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1814,7 +1856,7 @@
         <v>21</v>
       </c>
       <c r="B69" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C69" t="s">
         <v>21</v>
@@ -1822,651 +1864,651 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B70" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C70" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B71" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C71" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B72" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="C72" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="B73" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B74" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C74" t="s">
-        <v>59</v>
+        <v>218</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B75" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="C75" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B76" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C76" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="B77" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C77" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="B78" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C78" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C79" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C80" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B81" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C81" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="B82" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C82" t="s">
-        <v>10</v>
+        <v>220</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C83" t="s">
-        <v>66</v>
+        <v>221</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B84" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C84" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B85" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C85" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="B86" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C86" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B87" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C87" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="B88" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C88" t="s">
-        <v>216</v>
+        <v>78</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="B89" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C89" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="B90" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="C90" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="B91" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C91" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B92" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C92" t="s">
-        <v>72</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C93" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B94" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C94" t="s">
-        <v>217</v>
+        <v>69</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B95" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C95" t="s">
-        <v>58</v>
+        <v>222</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="B96" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B97" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C97" t="s">
-        <v>66</v>
+        <v>215</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="B98" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C98" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B99" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C99" t="s">
-        <v>218</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="B100" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C100" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B101" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C101" t="s">
-        <v>76</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="B102" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C102" t="s">
-        <v>77</v>
+        <v>216</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B103" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C103" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B104" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="C104" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B105" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C105" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B106" t="s">
         <v>179</v>
       </c>
       <c r="C106" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="B107" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="C107" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="B108" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C108" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B109" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C109" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B110" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C110" t="s">
-        <v>80</v>
+        <v>223</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="B111" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C111" t="s">
-        <v>219</v>
+        <v>27</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="B112" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C112" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="B113" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="C113" t="s">
-        <v>79</v>
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B114" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C114" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B115" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="C115" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="B116" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="C116" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B117" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C117" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B118" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C118" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B119" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="C119" t="s">
-        <v>221</v>
+        <v>82</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="B120" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C120" t="s">
-        <v>171</v>
+        <v>225</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B121" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C121" t="s">
-        <v>153</v>
+        <v>215</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B122" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C122" t="s">
-        <v>88</v>
+        <v>226</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B123" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C123" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="B124" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C124" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B125" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C125" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="B126" t="s">
         <v>191</v>
       </c>
       <c r="C126" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B127" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="C127" t="s">
-        <v>91</v>
+        <v>227</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B128" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C128" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2474,263 +2516,263 @@
         <v>92</v>
       </c>
       <c r="B129" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C129" t="s">
-        <v>40</v>
+        <v>215</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="B130" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C130" t="s">
-        <v>93</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="B131" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="C131" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B132" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C132" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="B133" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C133" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="B134" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="C134" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B135" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C135" t="s">
-        <v>68</v>
+        <v>228</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="B136" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C136" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="B137" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C137" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="B138" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C138" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B139" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C139" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="B140" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C140" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B141" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C141" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B142" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C142" t="s">
-        <v>102</v>
+        <v>203</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="B143" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="C143" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="B144" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C144" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>103</v>
+        <v>36</v>
       </c>
       <c r="B145" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C145" t="s">
-        <v>103</v>
+        <v>36</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B146" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C146" t="s">
-        <v>104</v>
+        <v>229</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="B147" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C147" t="s">
-        <v>76</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="B148" t="s">
         <v>179</v>
       </c>
       <c r="C148" t="s">
-        <v>43</v>
+        <v>230</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="B149" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C149" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="B150" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="C150" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B151" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C151" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="B152" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C152" t="s">
-        <v>38</v>
+        <v>231</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2738,10 +2780,10 @@
         <v>107</v>
       </c>
       <c r="B153" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C153" t="s">
-        <v>107</v>
+        <v>214</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2749,76 +2791,76 @@
         <v>108</v>
       </c>
       <c r="B154" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C154" t="s">
-        <v>171</v>
+        <v>108</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="B155" t="s">
         <v>179</v>
       </c>
       <c r="C155" t="s">
-        <v>109</v>
+        <v>14</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="B156" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C156" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B157" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="C157" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B158" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C158" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="B159" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C159" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="B160" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C160" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -2826,10 +2868,10 @@
         <v>112</v>
       </c>
       <c r="B161" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="C161" t="s">
-        <v>222</v>
+        <v>112</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -2837,10 +2879,10 @@
         <v>113</v>
       </c>
       <c r="B162" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="C162" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -2848,7 +2890,7 @@
         <v>114</v>
       </c>
       <c r="B163" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C163" t="s">
         <v>114</v>
@@ -2859,21 +2901,21 @@
         <v>115</v>
       </c>
       <c r="B164" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C164" t="s">
-        <v>115</v>
+        <v>232</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B165" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C165" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -2881,10 +2923,10 @@
         <v>116</v>
       </c>
       <c r="B166" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="C166" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -2892,43 +2934,43 @@
         <v>117</v>
       </c>
       <c r="B167" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C167" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="B168" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C168" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B169" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C169" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="B170" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C170" t="s">
-        <v>10</v>
+        <v>233</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -2936,10 +2978,10 @@
         <v>120</v>
       </c>
       <c r="B171" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C171" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -2947,7 +2989,7 @@
         <v>121</v>
       </c>
       <c r="B172" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="C172" t="s">
         <v>121</v>
@@ -2955,816 +2997,816 @@
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>122</v>
+        <v>10</v>
       </c>
       <c r="B173" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C173" t="s">
-        <v>122</v>
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B174" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C174" t="s">
-        <v>223</v>
+        <v>122</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="B175" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="B176" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C176" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B177" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="C177" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="B178" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C178" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="B179" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C179" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="B180" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C180" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B181" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C181" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="C182" t="s">
-        <v>15</v>
+        <v>208</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C183" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>61</v>
+        <v>128</v>
       </c>
       <c r="B184" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="C184" t="s">
-        <v>61</v>
+        <v>128</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="B185" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C185" t="s">
-        <v>14</v>
+        <v>129</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B186" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C186" t="s">
-        <v>10</v>
+        <v>205</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B187" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C187" t="s">
-        <v>128</v>
+        <v>206</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B188" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C188" t="s">
-        <v>21</v>
+        <v>208</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="B189" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C189" t="s">
-        <v>129</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="B190" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="C190" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C191" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B192" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B193" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C193" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B194" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="C194" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B195" t="s">
         <v>182</v>
       </c>
       <c r="C195" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B196" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C196" t="s">
-        <v>222</v>
+        <v>134</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="B197" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C197" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="B198" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C198" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="B199" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C199" t="s">
-        <v>116</v>
+        <v>234</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B200" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C200" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="B201" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C201" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B202" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C202" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="B203" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C203" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B204" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C204" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B205" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="C205" t="s">
-        <v>137</v>
+        <v>235</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>27</v>
+        <v>139</v>
       </c>
       <c r="B206" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C206" t="s">
-        <v>27</v>
+        <v>139</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B207" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C207" t="s">
-        <v>206</v>
+        <v>27</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B208" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C208" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B209" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C209" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>140</v>
+        <v>5</v>
       </c>
       <c r="B210" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C210" t="s">
-        <v>140</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="B211" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C211" t="s">
-        <v>141</v>
+        <v>10</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="B212" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C212" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="B213" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C213" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="B214" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C214" t="s">
-        <v>27</v>
+        <v>236</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="B215" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C215" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>23</v>
+        <v>145</v>
       </c>
       <c r="B216" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C216" t="s">
-        <v>23</v>
+        <v>145</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>43</v>
+        <v>146</v>
       </c>
       <c r="B217" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="C217" t="s">
-        <v>43</v>
+        <v>206</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="B218" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C218" t="s">
-        <v>105</v>
+        <v>237</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="B219" t="s">
         <v>189</v>
       </c>
       <c r="C219" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B220" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C220" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B221" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C221" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>15</v>
+        <v>124</v>
       </c>
       <c r="B222" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C222" t="s">
-        <v>15</v>
+        <v>124</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="B223" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C223" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B224" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C224" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>33</v>
+        <v>151</v>
       </c>
       <c r="B225" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="C225" t="s">
-        <v>33</v>
+        <v>151</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>145</v>
+        <v>27</v>
       </c>
       <c r="B226" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="C226" t="s">
-        <v>224</v>
+        <v>27</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>10</v>
+        <v>152</v>
       </c>
       <c r="B227" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C227" t="s">
-        <v>10</v>
+        <v>152</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="B228" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C228" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="B229" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C229" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B230" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C230" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="B231" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C231" t="s">
-        <v>146</v>
+        <v>91</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B232" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="C232" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>15</v>
+        <v>155</v>
       </c>
       <c r="B233" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C233" t="s">
-        <v>15</v>
+        <v>239</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="B234" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C234" t="s">
-        <v>147</v>
+        <v>21</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="B235" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="C235" t="s">
-        <v>10</v>
+        <v>240</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="B236" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C236" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B237" t="s">
         <v>179</v>
       </c>
       <c r="C237" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="B238" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C238" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="B239" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="C239" t="s">
-        <v>79</v>
+        <v>154</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B240" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C240" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B241" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C241" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="B242" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="C242" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="B243" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C243" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="B244" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C244" t="s">
-        <v>219</v>
+        <v>56</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="B245" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C245" t="s">
-        <v>88</v>
+        <v>167</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" t="s">
-        <v>151</v>
+        <v>27</v>
       </c>
       <c r="B246" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C246" t="s">
-        <v>151</v>
+        <v>27</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -3772,670 +3814,307 @@
         <v>152</v>
       </c>
       <c r="B247" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C247" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B248" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C248" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B249" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="C249" t="s">
-        <v>225</v>
+        <v>162</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>38</v>
+        <v>163</v>
       </c>
       <c r="B250" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C250" t="s">
-        <v>38</v>
+        <v>163</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B251" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="C251" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="B252" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="C252" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>111</v>
+        <v>164</v>
       </c>
       <c r="B253" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C253" t="s">
-        <v>111</v>
+        <v>241</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="B254" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C254" t="s">
-        <v>21</v>
+        <v>231</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="B255" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C255" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="B256" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C256" t="s">
-        <v>171</v>
+        <v>208</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B257" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C257" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>157</v>
+        <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C258" t="s">
-        <v>157</v>
+        <v>207</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="B259" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="C259" t="s">
-        <v>23</v>
+        <v>167</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="B260" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C260" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="B261" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C261" t="s">
-        <v>21</v>
+        <v>168</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="B262" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C262" t="s">
-        <v>158</v>
+        <v>69</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B263" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C263" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>23</v>
+        <v>170</v>
       </c>
       <c r="B264" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C264" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="B265" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C265" t="s">
-        <v>98</v>
+        <v>171</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="B266" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C266" t="s">
-        <v>160</v>
+        <v>221</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B267" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C267" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>162</v>
+        <v>10</v>
       </c>
       <c r="B268" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C268" t="s">
-        <v>162</v>
+        <v>10</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B269" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C269" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="B270" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C270" t="s">
-        <v>171</v>
+        <v>10</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="B271" t="s">
         <v>186</v>
       </c>
       <c r="C271" t="s">
-        <v>88</v>
+        <v>207</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="B272" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C272" t="s">
-        <v>140</v>
+        <v>175</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="B273" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C273" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="B274" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C274" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3">
-      <c r="A275" t="s">
-        <v>164</v>
-      </c>
-      <c r="B275" t="s">
-        <v>193</v>
-      </c>
-      <c r="C275" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3">
-      <c r="A276" t="s">
-        <v>61</v>
-      </c>
-      <c r="B276" t="s">
-        <v>182</v>
-      </c>
-      <c r="C276" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3">
-      <c r="A277" t="s">
-        <v>62</v>
-      </c>
-      <c r="B277" t="s">
-        <v>179</v>
-      </c>
-      <c r="C277" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3">
-      <c r="A278" t="s">
-        <v>165</v>
-      </c>
-      <c r="B278" t="s">
-        <v>191</v>
-      </c>
-      <c r="C278" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3">
-      <c r="A279" t="s">
-        <v>166</v>
-      </c>
-      <c r="B279" t="s">
-        <v>195</v>
-      </c>
-      <c r="C279" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3">
-      <c r="A280" t="s">
-        <v>17</v>
-      </c>
-      <c r="B280" t="s">
-        <v>187</v>
-      </c>
-      <c r="C280" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3">
-      <c r="A281" t="s">
-        <v>87</v>
-      </c>
-      <c r="B281" t="s">
-        <v>179</v>
-      </c>
-      <c r="C281" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3">
-      <c r="A282" t="s">
-        <v>10</v>
-      </c>
-      <c r="B282" t="s">
-        <v>182</v>
-      </c>
-      <c r="C282" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3">
-      <c r="A283" t="s">
-        <v>167</v>
-      </c>
-      <c r="B283" t="s">
-        <v>193</v>
-      </c>
-      <c r="C283" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3">
-      <c r="A284" t="s">
-        <v>88</v>
-      </c>
-      <c r="B284" t="s">
-        <v>186</v>
-      </c>
-      <c r="C284" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3">
-      <c r="A285" t="s">
-        <v>168</v>
-      </c>
-      <c r="B285" t="s">
-        <v>180</v>
-      </c>
-      <c r="C285" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3">
-      <c r="A286" t="s">
-        <v>10</v>
-      </c>
-      <c r="B286" t="s">
-        <v>182</v>
-      </c>
-      <c r="C286" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3">
-      <c r="A287" t="s">
-        <v>169</v>
-      </c>
-      <c r="B287" t="s">
-        <v>186</v>
-      </c>
-      <c r="C287" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3">
-      <c r="A288" t="s">
-        <v>21</v>
-      </c>
-      <c r="B288" t="s">
-        <v>182</v>
-      </c>
-      <c r="C288" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3">
-      <c r="A289" t="s">
-        <v>170</v>
-      </c>
-      <c r="B289" t="s">
-        <v>186</v>
-      </c>
-      <c r="C289" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3">
-      <c r="A290" t="s">
-        <v>16</v>
-      </c>
-      <c r="B290" t="s">
-        <v>183</v>
-      </c>
-      <c r="C290" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3">
-      <c r="A291" t="s">
-        <v>171</v>
-      </c>
-      <c r="B291" t="s">
-        <v>187</v>
-      </c>
-      <c r="C291" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3">
-      <c r="A292" t="s">
-        <v>38</v>
-      </c>
-      <c r="B292" t="s">
-        <v>188</v>
-      </c>
-      <c r="C292" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3">
-      <c r="A293" t="s">
-        <v>33</v>
-      </c>
-      <c r="B293" t="s">
-        <v>193</v>
-      </c>
-      <c r="C293" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3">
-      <c r="A294" t="s">
-        <v>172</v>
-      </c>
-      <c r="B294" t="s">
-        <v>198</v>
-      </c>
-      <c r="C294" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3">
-      <c r="A295" t="s">
-        <v>173</v>
-      </c>
-      <c r="B295" t="s">
-        <v>179</v>
-      </c>
-      <c r="C295" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3">
-      <c r="A296" t="s">
-        <v>27</v>
-      </c>
-      <c r="B296" t="s">
-        <v>182</v>
-      </c>
-      <c r="C296" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3">
-      <c r="A297" t="s">
-        <v>88</v>
-      </c>
-      <c r="B297" t="s">
-        <v>186</v>
-      </c>
-      <c r="C297" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3">
-      <c r="A298" t="s">
-        <v>174</v>
-      </c>
-      <c r="B298" t="s">
-        <v>179</v>
-      </c>
-      <c r="C298" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3">
-      <c r="A299" t="s">
-        <v>175</v>
-      </c>
-      <c r="B299" t="s">
-        <v>180</v>
-      </c>
-      <c r="C299" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3">
-      <c r="A300" t="s">
-        <v>33</v>
-      </c>
-      <c r="B300" t="s">
-        <v>193</v>
-      </c>
-      <c r="C300" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3">
-      <c r="A301" t="s">
-        <v>176</v>
-      </c>
-      <c r="B301" t="s">
-        <v>198</v>
-      </c>
-      <c r="C301" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3">
-      <c r="A302" t="s">
         <v>177</v>
-      </c>
-      <c r="B302" t="s">
-        <v>182</v>
-      </c>
-      <c r="C302" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3">
-      <c r="A303" t="s">
-        <v>178</v>
-      </c>
-      <c r="B303" t="s">
-        <v>183</v>
-      </c>
-      <c r="C303" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3">
-      <c r="A304" t="s">
-        <v>21</v>
-      </c>
-      <c r="B304" t="s">
-        <v>182</v>
-      </c>
-      <c r="C304" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3">
-      <c r="A305" t="s">
-        <v>22</v>
-      </c>
-      <c r="B305" t="s">
-        <v>179</v>
-      </c>
-      <c r="C305" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3">
-      <c r="A306" t="s">
-        <v>10</v>
-      </c>
-      <c r="B306" t="s">
-        <v>182</v>
-      </c>
-      <c r="C306" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3">
-      <c r="A307" t="s">
-        <v>52</v>
-      </c>
-      <c r="B307" t="s">
-        <v>179</v>
-      </c>
-      <c r="C307" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
